--- a/education_forms/038_education_librarian_job_application_form--education_forms.xlsx
+++ b/education_forms/038_education_librarian_job_application_form--education_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,18 +510,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input_1</t>
+          <t>highest_education_level</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your highest level of education completed?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please specify your highest completed education level</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,38 +537,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>work_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your current or most recent work experience in education or related fields?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide a brief description of your experience</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_input_3</t>
+          <t>expertise_lib_management_systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your expertise in library management systems or information technologies?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe any relevant experience or certifications with specific systems</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -574,43 +586,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_input_4</t>
+          <t>professional_certifications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Do you hold any professional certifications or licenses?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List any relevant certifications or licenses</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_input_5</t>
+          <t>availability_shifts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your availability for working hours, considering any flexible or standard shifts?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please specify any specific shifts you are available or flexible</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,18 +645,130 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_input_6</t>
+          <t>pressure_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate your ability to work well under pressure in a fast-paced environment?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate from 1 to 10, where 1 is low and 10 is high</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>collection_management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Do you have experience with collection management and cataloging processes?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe any relevant experience or certifications</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>resource_sharing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Are you familiar with library-specific software and platforms for resource sharing and discovery?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>List any specific platforms or systems you are familiar with</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>teaching_research</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>How many years of experience do you have with teaching or academic research?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Specify the exact number of years</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>areas_of_knowledge</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What specific areas of knowledge or skills do you bring to the role of an education librarian?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Be specific and provide examples</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
